--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486690_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486690_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.083</v>
+        <v>7.2749</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3432</v>
+        <v>5.2056</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7398</v>
+        <v>2.0694</v>
       </c>
       <c r="G2" t="n">
         <v>4.8839</v>
@@ -610,13 +610,13 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>3.084</v>
+        <v>1.2759</v>
       </c>
       <c r="T2" t="n">
-        <v>2.537</v>
+        <v>1.3993</v>
       </c>
       <c r="U2" t="n">
-        <v>0.547</v>
+        <v>-0.1234</v>
       </c>
       <c r="V2" t="n">
         <v>4.0113</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0108</v>
+        <v>3.7032</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1111</v>
+        <v>2.58</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8997000000000001</v>
+        <v>1.1232</v>
       </c>
       <c r="G3" t="n">
         <v>5.6795</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3751</v>
+        <v>0.3173</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3864</v>
+        <v>0.0825</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0113</v>
+        <v>0.2348</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9885</v>
+        <v>3.2573</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5406</v>
+        <v>1.0578</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4478</v>
+        <v>2.1995</v>
       </c>
       <c r="G4" t="n">
         <v>1.7995</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3587</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4415</v>
+        <v>0.0757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8002</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3282</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8764</v>
+        <v>2.3931</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0674</v>
+        <v>3.1114</v>
       </c>
       <c r="F5" t="n">
-        <v>1.809</v>
+        <v>-0.7183</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4464</v>
+        <v>2.1448</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0621</v>
+        <v>0.2616</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3843</v>
+        <v>1.8832</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.594</v>
+        <v>2.1875</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5579</v>
+        <v>-0.2202</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0361</v>
+        <v>2.4077</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0404</v>
+        <v>-0.0427</v>
       </c>
       <c r="N5" t="n">
-        <v>0.62</v>
+        <v>0.4818</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4205</v>
+        <v>-0.5245</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1018</v>
+        <v>0.4414</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6269</v>
+        <v>0.6616</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4749</v>
+        <v>-0.2202</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.257</v>
+        <v>2.3672</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0542</v>
+        <v>2.0402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2028</v>
+        <v>0.327</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2014</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0203</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3038</v>
+        <v>0.6822</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7165</v>
+        <v>-0.5923</v>
       </c>
       <c r="V6" t="n">
         <v>1.5133</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1629</v>
+        <v>0.9538</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2288</v>
+        <v>-0.6565</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.066</v>
+        <v>1.6103</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1448</v>
+        <v>0.4464</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2616</v>
+        <v>0.0621</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8832</v>
+        <v>0.3843</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1875</v>
+        <v>-0.594</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2202</v>
+        <v>-0.5579</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4077</v>
+        <v>-0.0361</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0427</v>
+        <v>1.0404</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4818</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5245</v>
+        <v>0.4205</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7887999999999999</v>
+        <v>1.1792</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.221</v>
+        <v>0.9029</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5678</v>
+        <v>0.2763</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>D. IYOHA OSARENKHOE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2564</v>
+        <v>0.3728</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4907</v>
+        <v>0.1855</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7471</v>
+        <v>0.1873</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4701</v>
+        <v>-0.2492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6413</v>
+        <v>0.5239</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1114</v>
+        <v>-0.7732</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6212</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3658</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9871</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1511</v>
+        <v>-0.3313</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2755</v>
+        <v>0.4826</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1244</v>
+        <v>-0.8138</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9542</v>
+        <v>-0.0344</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1306</v>
+        <v>0.1034</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1763</v>
+        <v>-0.1378</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. IYOHA OSARENKHOE</t>
+          <t>P. REYES ZUR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2198</v>
+        <v>-0.2374</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08210000000000001</v>
+        <v>-1.1307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1377</v>
+        <v>0.8933</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2492</v>
+        <v>0.2827</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5239</v>
+        <v>0.5517</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7732</v>
+        <v>-0.269</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.3443</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0414</v>
+        <v>0.3451</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>-0.6895</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3313</v>
+        <v>0.6271</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4826</v>
+        <v>0.2066</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8138</v>
+        <v>0.4205</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1875</v>
+        <v>0.1517</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1791</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1875</v>
+        <v>-0.0274</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. REYES ZUR</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2292</v>
+        <v>-0.2633</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9238</v>
+        <v>-1.1594</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6946</v>
+        <v>0.8961</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2827</v>
+        <v>-1.4701</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5517</v>
+        <v>0.6413</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.269</v>
+        <v>-2.1114</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3443</v>
+        <v>-1.6212</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3451</v>
+        <v>0.3658</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6895</v>
+        <v>-1.9871</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6271</v>
+        <v>0.1511</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2066</v>
+        <v>0.2755</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4205</v>
+        <v>-0.1244</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1599</v>
+        <v>0.4345</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3859</v>
+        <v>0.4618</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2261</v>
+        <v>-0.0274</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8044</v>
+        <v>-1.0691</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0421</v>
+        <v>-2.4557</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2376</v>
+        <v>1.3866</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1253</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5405</v>
+        <v>0.2759</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8547</v>
+        <v>0.441</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3141</v>
+        <v>-0.1651</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5712</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3481</v>
+        <v>-3.6239</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2958</v>
+        <v>-2.4475</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0523</v>
+        <v>-1.1764</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1336</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8829</v>
+        <v>0.607</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9926</v>
+        <v>0.8409</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1097</v>
+        <v>-0.2339</v>
       </c>
       <c r="V12" t="n">
         <v>0.5712</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8948</v>
+        <v>-5.2743</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.76</v>
+        <v>-2.1395</v>
       </c>
       <c r="F13" t="n">
         <v>-3.1348</v>
@@ -1468,10 +1468,10 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.331</v>
+        <v>0.2896</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2485</v>
+        <v>0.372</v>
       </c>
       <c r="U13" t="n">
         <v>-0.0825</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.5783</v>
+        <v>9.854299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.915000000000003</v>
+        <v>4.191199999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>5.663</v>
+        <v>5.6632</v>
       </c>
       <c r="G14" t="n">
         <v>9.6205</v>
@@ -1525,16 +1525,16 @@
         <v>8.282299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.3053</v>
+        <v>-2.305299999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6433</v>
+        <v>3.643300000000001</v>
       </c>
       <c r="N14" t="n">
         <v>4.129899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4864</v>
+        <v>-0.4863999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-5.7925</v>
@@ -1546,19 +1546,19 @@
         <v>10.6192</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3793</v>
+        <v>5.6555</v>
       </c>
       <c r="T14" t="n">
-        <v>5.926500000000001</v>
+        <v>6.202400000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5470999999999998</v>
+        <v>-0.5470000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>0.3709000000000007</v>
       </c>
       <c r="W14" t="n">
-        <v>8.423300000000001</v>
+        <v>8.423299999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-8.0524</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3797</v>
+        <v>5.541</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5147</v>
+        <v>3.9284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.865</v>
+        <v>1.6126</v>
       </c>
       <c r="G15" t="n">
         <v>2.8414</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1681</v>
+        <v>-1.0068</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1588</v>
+        <v>-0.7451</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0092</v>
+        <v>-0.2616</v>
       </c>
       <c r="V15" t="n">
         <v>2.741</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7914</v>
+        <v>3.3457</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1966</v>
+        <v>0.6103</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5948</v>
+        <v>2.7354</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7339</v>
@@ -1702,13 +1702,13 @@
         <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1545</v>
+        <v>0.3998</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3039</v>
+        <v>0.1098</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1495</v>
+        <v>0.29</v>
       </c>
       <c r="V16" t="n">
         <v>1.5559</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2369</v>
+        <v>1.2308</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7475</v>
+        <v>0.2666</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5106</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6152</v>
+        <v>0.6585</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2687</v>
+        <v>-0.9443</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8839</v>
+        <v>1.6028</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4102</v>
+        <v>0.5013</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8359</v>
+        <v>-0.116</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5743</v>
+        <v>0.6172</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.795</v>
+        <v>0.1573</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1046</v>
+        <v>-0.8283</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3096</v>
+        <v>0.9856</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>2.51</v>
+        <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5831</v>
+        <v>0.3446</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0677</v>
+        <v>0.4684</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4847</v>
+        <v>-0.1238</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.5406</v>
+        <v>0.6138</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2004</v>
+        <v>1.2277</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.741</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0421</v>
+        <v>-0.1794</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1471</v>
+        <v>-0.5171</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1892</v>
+        <v>0.3378</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6585</v>
+        <v>-0.7104</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9443</v>
+        <v>-0.0276</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6028</v>
+        <v>-0.6827</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5013</v>
+        <v>-0.6481</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.116</v>
+        <v>0.0414</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6172</v>
+        <v>-0.6895</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1573</v>
+        <v>-0.0623</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9856</v>
+        <v>0.0068</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8442</v>
+        <v>0.1448</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0547</v>
+        <v>0.131</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8989</v>
+        <v>0.0139</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>J. BARRIOS RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3462</v>
+        <v>-1.0048</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6206</v>
+        <v>-1.188</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2744</v>
+        <v>0.1832</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7104</v>
+        <v>-1.5123</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0276</v>
+        <v>-1.0896</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6827</v>
+        <v>-0.4227</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6481</v>
+        <v>-1.1741</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0414</v>
+        <v>-0.6067</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6895</v>
+        <v>-0.5674</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0623</v>
+        <v>-0.3382</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.4829</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0068</v>
+        <v>0.1447</v>
       </c>
       <c r="P19" t="n">
         <v>0.3862</v>
@@ -1936,28 +1936,28 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.022</v>
+        <v>-0.2069</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0275</v>
+        <v>-0.0139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0495</v>
+        <v>-0.193</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BARRIOS RUIZ</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2613</v>
+        <v>-1.1602</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3948</v>
+        <v>0.1961</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1335</v>
+        <v>-1.3563</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5123</v>
+        <v>0.6152</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0896</v>
+        <v>-0.2687</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4227</v>
+        <v>0.8839</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1741</v>
+        <v>1.4102</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6067</v>
+        <v>0.8359</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5674</v>
+        <v>0.5743</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3382</v>
+        <v>-0.795</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4829</v>
+        <v>-1.1046</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1447</v>
+        <v>0.3096</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3862</v>
+        <v>2.51</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4634</v>
+        <v>0.186</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2207</v>
+        <v>0.5164</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2427</v>
+        <v>-0.3304</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3282</v>
+        <v>-2.5406</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2004</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3282</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4582</v>
+        <v>-1.3593</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2205</v>
+        <v>-2.0959</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2377</v>
+        <v>0.7366</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5314</v>
+        <v>-4.1734</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7176</v>
+        <v>-4.9782</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8138</v>
+        <v>0.8048</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6481</v>
+        <v>-2.896</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0414</v>
+        <v>-3.3912</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6895</v>
+        <v>0.4952</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8833</v>
+        <v>-1.2774</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.759</v>
+        <v>-1.587</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1244</v>
+        <v>0.3096</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3862</v>
+        <v>2.7031</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.004</v>
+        <v>-0.676</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.607</v>
+        <v>0.0132</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.397</v>
+        <v>-0.6891</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6565</v>
+        <v>3.6831</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6831</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CABRERA CABRERA</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7255</v>
+        <v>-1.9852</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3652</v>
+        <v>-1.9102</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3603</v>
+        <v>-0.075</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8068</v>
+        <v>-1.5314</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4066</v>
+        <v>-0.7176</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4002</v>
+        <v>-0.8138</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3376</v>
+        <v>-0.6481</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3376</v>
+        <v>0.0414</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6895</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4692</v>
+        <v>-0.8833</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.759</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4002</v>
+        <v>-0.1244</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2703</v>
+        <v>-0.531</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0277</v>
+        <v>-0.2967</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2427</v>
+        <v>-0.2343</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>D. CABRERA CABRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8072</v>
+        <v>-2.4346</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1302</v>
+        <v>-1.2618</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3229</v>
+        <v>-1.1728</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1734</v>
+        <v>-1.8068</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.9782</v>
+        <v>-1.4066</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8048</v>
+        <v>-0.4002</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.896</v>
+        <v>-1.3376</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.3912</v>
+        <v>-1.3376</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4952</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2774</v>
+        <v>-0.4692</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.587</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3096</v>
+        <v>-0.4002</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7031</v>
+        <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1239</v>
+        <v>0.0206</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.021</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1028</v>
+        <v>-0.0551</v>
       </c>
       <c r="V23" t="n">
-        <v>3.6831</v>
+        <v>-1.2277</v>
       </c>
       <c r="W23" t="n">
-        <v>3.6831</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8794</v>
+        <v>-3.3139</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9401</v>
+        <v>-1.6641</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9393</v>
+        <v>-1.6498</v>
       </c>
       <c r="G24" t="n">
         <v>-1.472</v>
@@ -2326,13 +2326,13 @@
         <v>2.7031</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2756</v>
+        <v>-0.1588</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0474</v>
+        <v>0.3234</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7718</v>
+        <v>-0.4823</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4554</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5504</v>
+        <v>-4.811</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3034</v>
+        <v>-2.0273</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2471</v>
+        <v>-2.7837</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7955</v>
@@ -2404,13 +2404,13 @@
         <v>2.1239</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1877</v>
+        <v>-0.4483</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6889</v>
+        <v>-0.0351</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8766</v>
+        <v>-0.4133</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7257</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.578100000000001</v>
+        <v>-6.1309</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6631</v>
+        <v>-5.663</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.9152</v>
+        <v>-0.4677999999999995</v>
       </c>
       <c r="G26" t="n">
         <v>-9.620600000000001</v>
@@ -2461,7 +2461,7 @@
         <v>-4.13</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4865000000000002</v>
+        <v>0.4864999999999997</v>
       </c>
       <c r="M26" t="n">
         <v>-5.9772</v>
@@ -2473,7 +2473,7 @@
         <v>2.3052</v>
       </c>
       <c r="P26" t="n">
-        <v>5.7924</v>
+        <v>5.792400000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-10.6194</v>
@@ -2482,13 +2482,13 @@
         <v>16.4118</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.3794</v>
+        <v>-1.932</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5471</v>
+        <v>0.5471999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.9264</v>
+        <v>-2.479</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3708999999999998</v>
